--- a/Result/profitability/5516.xlsx
+++ b/Result/profitability/5516.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1150000000000001</v>
+        <v>-0.1212500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>4.5875</v>
+        <v>4.0025</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.04</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1062500000000001</v>
+        <v>0.07624999999999989</v>
       </c>
       <c r="N3" t="n">
-        <v>5.172499999999999</v>
+        <v>6.0725</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09749999999999989</v>
+        <v>0.1624999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>7.7125</v>
+        <v>8.305</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2037499999999999</v>
+        <v>0.1662499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9.39875</v>
+        <v>8.922499999999999</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.03</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1799999999999999</v>
+        <v>0.07874999999999989</v>
       </c>
       <c r="N6" t="n">
-        <v>8.963749999999999</v>
+        <v>7.6275</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1012499999999999</v>
+        <v>0.1137499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>8.17375</v>
+        <v>8.272500000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1437499999999999</v>
+        <v>0.06499999999999989</v>
       </c>
       <c r="N8" t="n">
-        <v>8.463750000000001</v>
+        <v>7.47</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.1362499999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>7.664999999999999</v>
+        <v>7.665</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.1562499999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>7.96875</v>
+        <v>7.968749999999999</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>0.2274999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>6.51</v>
+        <v>6.509999999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.2087499999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>5.41875</v>
+        <v>5.418749999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5516</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>670</v>
+      </c>
+      <c r="D75" t="n">
+        <v>653</v>
+      </c>
+      <c r="E75" t="n">
+        <v>17</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.1162500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-1.145454545454546</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-7.950000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.7593123209169055</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.363636363636364</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.81</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.6018957345971564</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
